--- a/results/2026-04-07-SAT-precedence-graph/results_sat_scl_cont_totalizer_prec_graph_120s.xlsx
+++ b/results/2026-04-07-SAT-precedence-graph/results_sat_scl_cont_totalizer_prec_graph_120s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="105">
   <si>
     <t>algorithm_time</t>
   </si>
@@ -370,6 +370,15 @@
   </si>
   <si>
     <t>stationB12</t>
+  </si>
+  <si>
+    <t>original average</t>
+  </si>
+  <si>
+    <t>track average</t>
+  </si>
+  <si>
+    <t>station average</t>
   </si>
 </sst>
 </file>
@@ -385,15 +394,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -401,12 +416,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -691,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z73"/>
+  <dimension ref="A1:AD73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -722,7 +754,7 @@
     <col min="26" max="26" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -801,8 +833,17 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AB1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.72480911800000003</v>
       </c>
@@ -881,8 +922,20 @@
       <c r="Z2">
         <v>6771</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AB2" s="2">
+        <f>AVERAGE(R2:R25)</f>
+        <v>525.46328333333338</v>
+      </c>
+      <c r="AC2" s="2">
+        <f>AVERAGE(R26:R49)</f>
+        <v>15783.073518583331</v>
+      </c>
+      <c r="AD2" s="2">
+        <f>AVERAGE(R50:R73)</f>
+        <v>22017.128170458291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5.3753015000000001E-2</v>
       </c>
@@ -962,7 +1015,7 @@
         <v>5882</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1.8352853999999998E-2</v>
       </c>
@@ -1042,7 +1095,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2.2568743999999901E-2</v>
       </c>
@@ -1122,7 +1175,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2.1249669999999998E-2</v>
       </c>
@@ -1202,7 +1255,7 @@
         <v>2634</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1.4906776E-2</v>
       </c>
@@ -1282,7 +1335,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1.5415610999999999E-2</v>
       </c>
@@ -1362,7 +1415,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.33893865200000001</v>
       </c>
@@ -1442,7 +1495,7 @@
         <v>23648</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>4.9265048999999901E-2</v>
       </c>
@@ -1522,7 +1575,7 @@
         <v>6574</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3.2181543999999999E-2</v>
       </c>
@@ -1602,7 +1655,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>6.2363808E-2</v>
       </c>
@@ -1682,7 +1735,7 @@
         <v>5090</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>6.1166705000000002E-2</v>
       </c>
@@ -1762,7 +1815,7 @@
         <v>4950</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1.2610253E-2</v>
       </c>
@@ -1842,7 +1895,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1.2203006999999899E-2</v>
       </c>
@@ -1922,7 +1975,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1.2157731999999999E-2</v>
       </c>
